--- a/src/fixtures/sample/gstr2b-2026-03.xlsx
+++ b/src/fixtures/sample/gstr2b-2026-03.xlsx
@@ -470,25 +470,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C6" t="str">
-        <v>S01/2026/061</v>
+        <v>S01/2026/063</v>
       </c>
       <c r="D6" t="str">
-        <v>10/03/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="E6">
-        <v>566400</v>
+        <v>556960</v>
       </c>
       <c r="F6">
-        <v>480000</v>
+        <v>472000</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>43200</v>
+        <v>42480</v>
       </c>
       <c r="I6">
-        <v>43200</v>
+        <v>42480</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>2026-04</v>
       </c>
       <c r="L6" t="str">
-        <v>16/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -511,31 +511,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>27AAPFM4821K1ZV</v>
+        <v>29AAKFK3390B1ZB</v>
       </c>
       <c r="B7" t="str">
-        <v>Mahesh Steel Traders</v>
+        <v>Kaveri Packaging</v>
       </c>
       <c r="C7" t="str">
-        <v>S01/2026/063</v>
+        <v>S03/2026/041</v>
       </c>
       <c r="D7" t="str">
-        <v>18/03/2026</v>
+        <v>22/01/2026</v>
       </c>
       <c r="E7">
-        <v>560500</v>
+        <v>129800</v>
       </c>
       <c r="F7">
-        <v>475000</v>
+        <v>110000</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>19800</v>
       </c>
       <c r="H7">
-        <v>42750</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>42750</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2026-04</v>
       </c>
       <c r="L7" t="str">
-        <v>12/04/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -564,19 +564,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C8" t="str">
-        <v>S03/2026/041</v>
+        <v>S03/2026/042</v>
       </c>
       <c r="D8" t="str">
-        <v>12/01/2026</v>
+        <v>18/01/2026</v>
       </c>
       <c r="E8">
-        <v>140420</v>
+        <v>126260</v>
       </c>
       <c r="F8">
-        <v>119000</v>
+        <v>107000</v>
       </c>
       <c r="G8">
-        <v>21420</v>
+        <v>19260</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2026-04</v>
       </c>
       <c r="L8" t="str">
-        <v>12/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -611,19 +611,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C9" t="str">
-        <v>S03/2026/042</v>
+        <v>S03/2026/051</v>
       </c>
       <c r="D9" t="str">
-        <v>22/01/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="E9">
-        <v>128620</v>
+        <v>134520</v>
       </c>
       <c r="F9">
-        <v>109000</v>
+        <v>114000</v>
       </c>
       <c r="G9">
-        <v>19620</v>
+        <v>20520</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2026-04</v>
       </c>
       <c r="L9" t="str">
-        <v>15/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -658,19 +658,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C10" t="str">
-        <v>S03/2026/051</v>
+        <v>S03/2026/052</v>
       </c>
       <c r="D10" t="str">
-        <v>19/02/2026</v>
+        <v>18/02/2026</v>
       </c>
       <c r="E10">
-        <v>132160</v>
+        <v>149860</v>
       </c>
       <c r="F10">
-        <v>112000</v>
+        <v>127000</v>
       </c>
       <c r="G10">
-        <v>20160</v>
+        <v>22860</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -705,19 +705,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C11" t="str">
-        <v>S03/2026/052</v>
+        <v>S03/2026/061</v>
       </c>
       <c r="D11" t="str">
-        <v>04/02/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="E11">
-        <v>133340</v>
+        <v>127440</v>
       </c>
       <c r="F11">
-        <v>113000</v>
+        <v>108000</v>
       </c>
       <c r="G11">
-        <v>20340</v>
+        <v>19440</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2026-04</v>
       </c>
       <c r="L11" t="str">
-        <v>15/04/2026</v>
+        <v>12/04/2026</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -752,19 +752,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C12" t="str">
-        <v>S03/2026/061</v>
+        <v>S03/2026/062</v>
       </c>
       <c r="D12" t="str">
-        <v>24/03/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="E12">
-        <v>127440</v>
+        <v>128620</v>
       </c>
       <c r="F12">
-        <v>108000</v>
+        <v>109000</v>
       </c>
       <c r="G12">
-        <v>19440</v>
+        <v>19620</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>2026-04</v>
       </c>
       <c r="L12" t="str">
-        <v>17/04/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
@@ -793,31 +793,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>29AAKFK3390B1ZB</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B13" t="str">
-        <v>Kaveri Packaging</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C13" t="str">
-        <v>S03/2026/062</v>
+        <v>SE 61</v>
       </c>
       <c r="D13" t="str">
-        <v>04/03/2026</v>
+        <v>03/03/2026</v>
       </c>
       <c r="E13">
-        <v>146320</v>
+        <v>155760</v>
       </c>
       <c r="F13">
-        <v>124000</v>
+        <v>132000</v>
       </c>
       <c r="G13">
-        <v>22320</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>11880</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>11880</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2026-04</v>
       </c>
       <c r="L13" t="str">
-        <v>17/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
@@ -849,22 +849,22 @@
         <v>SE 61</v>
       </c>
       <c r="D14" t="str">
-        <v>21/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="E14">
-        <v>162840</v>
+        <v>171100</v>
       </c>
       <c r="F14">
-        <v>138000</v>
+        <v>145000</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>12420</v>
+        <v>13050</v>
       </c>
       <c r="I14">
-        <v>12420</v>
+        <v>13050</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>2026-04</v>
       </c>
       <c r="L14" t="str">
-        <v>16/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
@@ -887,31 +887,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>27AAJFN2276C1ZC</v>
       </c>
       <c r="B15" t="str">
-        <v>Surya Electricals</v>
+        <v>Nilkanth Traders</v>
       </c>
       <c r="C15" t="str">
-        <v>SE 61</v>
+        <v>S07/2026/061</v>
       </c>
       <c r="D15" t="str">
-        <v>17/03/2026</v>
+        <v>25/03/2026</v>
       </c>
       <c r="E15">
-        <v>174640</v>
+        <v>243080</v>
       </c>
       <c r="F15">
-        <v>148000</v>
+        <v>206000</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>13320</v>
+        <v>18540</v>
       </c>
       <c r="I15">
-        <v>13320</v>
+        <v>18540</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>Nilkanth Traders</v>
       </c>
       <c r="C16" t="str">
-        <v>S07/2026/061</v>
+        <v>S07/2026/062</v>
       </c>
       <c r="D16" t="str">
-        <v>07/03/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="E16">
-        <v>228920</v>
+        <v>246620</v>
       </c>
       <c r="F16">
-        <v>194000</v>
+        <v>209000</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>17460</v>
+        <v>18810</v>
       </c>
       <c r="I16">
-        <v>17460</v>
+        <v>18810</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>2026-04</v>
       </c>
       <c r="L16" t="str">
-        <v>08/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="M16" t="str">
         <v>Yes</v>
@@ -981,31 +981,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>27AAJFN2276C1ZC</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B17" t="str">
-        <v>Nilkanth Traders</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C17" t="str">
-        <v>S07/2026/062</v>
+        <v>S08/2026/061</v>
       </c>
       <c r="D17" t="str">
-        <v>11/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="E17">
-        <v>243080</v>
+        <v>221840</v>
       </c>
       <c r="F17">
-        <v>206000</v>
+        <v>188000</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>33840</v>
       </c>
       <c r="H17">
-        <v>18540</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>18540</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>2026-04</v>
       </c>
       <c r="L17" t="str">
-        <v>13/04/2026</v>
+        <v>12/04/2026</v>
       </c>
       <c r="M17" t="str">
         <v>Yes</v>
@@ -1034,19 +1034,19 @@
         <v>Ratna Chemicals</v>
       </c>
       <c r="C18" t="str">
-        <v>S08/2026/061</v>
+        <v>S08/2026/062</v>
       </c>
       <c r="D18" t="str">
-        <v>26/03/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="E18">
-        <v>215940</v>
+        <v>217120</v>
       </c>
       <c r="F18">
-        <v>183000</v>
+        <v>184000</v>
       </c>
       <c r="G18">
-        <v>32940</v>
+        <v>33120</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1075,31 +1075,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAACM6543N1Z3</v>
       </c>
       <c r="B19" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Metro Motors</v>
       </c>
       <c r="C19" t="str">
-        <v>S08/2026/062</v>
+        <v>S09/2026/061</v>
       </c>
       <c r="D19" t="str">
-        <v>12/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="E19">
-        <v>199420</v>
+        <v>1041940</v>
       </c>
       <c r="F19">
-        <v>169000</v>
+        <v>883000</v>
       </c>
       <c r="G19">
-        <v>30420</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>79470</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>79470</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1108,13 +1108,13 @@
         <v>2026-04</v>
       </c>
       <c r="L19" t="str">
-        <v>15/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="M19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>ITC unavailable - blocked credit</v>
       </c>
       <c r="O19" t="str">
         <v>N</v>
@@ -1122,31 +1122,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>27AAACM6543N1Z3</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B20" t="str">
-        <v>Metro Motors</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C20" t="str">
-        <v>S09/2026/061</v>
+        <v>S10/2026/061</v>
       </c>
       <c r="D20" t="str">
-        <v>03/03/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="E20">
-        <v>1062000</v>
+        <v>316240</v>
       </c>
       <c r="F20">
-        <v>900000</v>
+        <v>268000</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>48240</v>
       </c>
       <c r="H20">
-        <v>81000</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>81000</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1155,13 +1155,13 @@
         <v>2026-04</v>
       </c>
       <c r="L20" t="str">
-        <v>15/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="M20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N20" t="str">
-        <v>ITC unavailable - blocked credit</v>
+        <v/>
       </c>
       <c r="O20" t="str">
         <v>N</v>
@@ -1175,19 +1175,19 @@
         <v>Vindhya Alloys</v>
       </c>
       <c r="C21" t="str">
-        <v>S10/2026/061</v>
+        <v>S10/2026/062</v>
       </c>
       <c r="D21" t="str">
-        <v>22/03/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="E21">
-        <v>311520</v>
+        <v>304440</v>
       </c>
       <c r="F21">
-        <v>264000</v>
+        <v>258000</v>
       </c>
       <c r="G21">
-        <v>47520</v>
+        <v>46440</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2026-04</v>
       </c>
       <c r="L21" t="str">
-        <v>10/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1216,31 +1216,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAHFS1129D1ZH</v>
       </c>
       <c r="B22" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Sahyadri Logistics</v>
       </c>
       <c r="C22" t="str">
-        <v>S10/2026/062</v>
+        <v>S11/2026/061</v>
       </c>
       <c r="D22" t="str">
-        <v>20/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="E22">
-        <v>316240</v>
+        <v>95580</v>
       </c>
       <c r="F22">
-        <v>268000</v>
+        <v>81000</v>
       </c>
       <c r="G22">
-        <v>48240</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>7290</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>7290</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>2026-04</v>
       </c>
       <c r="L22" t="str">
-        <v>10/04/2026</v>
+        <v>09/04/2026</v>
       </c>
       <c r="M22" t="str">
         <v>Yes</v>
@@ -1269,25 +1269,25 @@
         <v>Sahyadri Logistics</v>
       </c>
       <c r="C23" t="str">
-        <v>S11/2026/061</v>
+        <v>S11/2026/062</v>
       </c>
       <c r="D23" t="str">
-        <v>07/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="E23">
-        <v>100300</v>
+        <v>89680</v>
       </c>
       <c r="F23">
-        <v>85000</v>
+        <v>76000</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>7650</v>
+        <v>6840</v>
       </c>
       <c r="I23">
-        <v>7650</v>
+        <v>6840</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2026-04</v>
       </c>
       <c r="L23" t="str">
-        <v>09/04/2026</v>
+        <v>15/04/2026</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
@@ -1310,31 +1310,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>27AAHFS1129D1ZH</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B24" t="str">
-        <v>Sahyadri Logistics</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C24" t="str">
-        <v>S11/2026/062</v>
+        <v>S12/2026/061</v>
       </c>
       <c r="D24" t="str">
-        <v>07/03/2026</v>
+        <v>06/03/2026</v>
       </c>
       <c r="E24">
-        <v>93220</v>
+        <v>186440</v>
       </c>
       <c r="F24">
-        <v>79000</v>
+        <v>158000</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>7110</v>
+        <v>14220</v>
       </c>
       <c r="I24">
-        <v>7110</v>
+        <v>14220</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2026-04</v>
       </c>
       <c r="L24" t="str">
-        <v>12/04/2026</v>
+        <v>15/04/2026</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1363,25 +1363,25 @@
         <v>Bharat Office Supplies</v>
       </c>
       <c r="C25" t="str">
-        <v>S12/2026/061</v>
+        <v>S12/2026/062</v>
       </c>
       <c r="D25" t="str">
-        <v>03/03/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="E25">
-        <v>181720</v>
+        <v>185260</v>
       </c>
       <c r="F25">
-        <v>154000</v>
+        <v>157000</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>13860</v>
+        <v>14130</v>
       </c>
       <c r="I25">
-        <v>13860</v>
+        <v>14130</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>2026-04</v>
       </c>
       <c r="L25" t="str">
-        <v>09/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1413,22 +1413,22 @@
         <v>S13/2026/061</v>
       </c>
       <c r="D26" t="str">
-        <v>02/03/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="E26">
-        <v>76700</v>
+        <v>74340</v>
       </c>
       <c r="F26">
-        <v>65000</v>
+        <v>63000</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>5850</v>
+        <v>5670</v>
       </c>
       <c r="I26">
-        <v>5850</v>
+        <v>5670</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>2026-04</v>
       </c>
       <c r="L26" t="str">
-        <v>15/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="M26" t="str">
         <v>Yes</v>
@@ -1460,7 +1460,7 @@
         <v>S14/2026/061</v>
       </c>
       <c r="D27" t="str">
-        <v>15/03/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="E27">
         <v>151040</v>
@@ -1484,7 +1484,7 @@
         <v>2026-04</v>
       </c>
       <c r="L27" t="str">
-        <v>10/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
@@ -1507,16 +1507,16 @@
         <v>S15/2026/061</v>
       </c>
       <c r="D28" t="str">
-        <v>25/03/2026</v>
+        <v>06/03/2026</v>
       </c>
       <c r="E28">
-        <v>41300</v>
+        <v>38940</v>
       </c>
       <c r="F28">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="G28">
-        <v>6300</v>
+        <v>5940</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>2026-04</v>
       </c>
       <c r="L28" t="str">
-        <v>11/04/2026</v>
+        <v>15/04/2026</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1554,16 +1554,16 @@
         <v>S15/2026/062</v>
       </c>
       <c r="D29" t="str">
-        <v>21/03/2026</v>
+        <v>06/03/2026</v>
       </c>
       <c r="E29">
-        <v>34220</v>
+        <v>48380</v>
       </c>
       <c r="F29">
-        <v>29000</v>
+        <v>41000</v>
       </c>
       <c r="G29">
-        <v>5220</v>
+        <v>7380</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>2026-04</v>
       </c>
       <c r="L29" t="str">
-        <v>12/04/2026</v>
+        <v>15/04/2026</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
@@ -1601,16 +1601,16 @@
         <v>S15/2026/063</v>
       </c>
       <c r="D30" t="str">
-        <v>12/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="E30">
-        <v>47200</v>
+        <v>48380</v>
       </c>
       <c r="F30">
-        <v>40000</v>
+        <v>41000</v>
       </c>
       <c r="G30">
-        <v>7200</v>
+        <v>7380</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1648,16 +1648,16 @@
         <v>S16/2026/061</v>
       </c>
       <c r="D31" t="str">
-        <v>25/03/2026</v>
+        <v>08/03/2026</v>
       </c>
       <c r="E31">
-        <v>69620</v>
+        <v>82600</v>
       </c>
       <c r="F31">
-        <v>59000</v>
+        <v>70000</v>
       </c>
       <c r="G31">
-        <v>10620</v>
+        <v>12600</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>2026-04</v>
       </c>
       <c r="L31" t="str">
-        <v>09/04/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="M31" t="str">
         <v>Yes</v>
@@ -1695,16 +1695,16 @@
         <v>S16/2026/062</v>
       </c>
       <c r="D32" t="str">
-        <v>08/03/2026</v>
+        <v>25/03/2026</v>
       </c>
       <c r="E32">
-        <v>74340</v>
+        <v>61360</v>
       </c>
       <c r="F32">
-        <v>63000</v>
+        <v>52000</v>
       </c>
       <c r="G32">
-        <v>11340</v>
+        <v>9360</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>2026-04</v>
       </c>
       <c r="L32" t="str">
-        <v>09/04/2026</v>
+        <v>12/04/2026</v>
       </c>
       <c r="M32" t="str">
         <v>Yes</v>
@@ -1742,16 +1742,16 @@
         <v>S17/2026/061</v>
       </c>
       <c r="D33" t="str">
-        <v>18/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="E33">
-        <v>59000</v>
+        <v>51920</v>
       </c>
       <c r="F33">
-        <v>50000</v>
+        <v>44000</v>
       </c>
       <c r="G33">
-        <v>9000</v>
+        <v>7920</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>2026-04</v>
       </c>
       <c r="L33" t="str">
-        <v>14/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="M33" t="str">
         <v>Yes</v>
@@ -1789,22 +1789,22 @@
         <v>S18/2026/061</v>
       </c>
       <c r="D34" t="str">
-        <v>20/03/2026</v>
+        <v>11/03/2026</v>
       </c>
       <c r="E34">
-        <v>165200</v>
+        <v>172280</v>
       </c>
       <c r="F34">
-        <v>140000</v>
+        <v>146000</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>12600</v>
+        <v>13140</v>
       </c>
       <c r="I34">
-        <v>12600</v>
+        <v>13140</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>2026-04</v>
       </c>
       <c r="L34" t="str">
-        <v>09/04/2026</v>
+        <v>15/04/2026</v>
       </c>
       <c r="M34" t="str">
         <v>Yes</v>
@@ -1836,22 +1836,22 @@
         <v>S18/2026/062</v>
       </c>
       <c r="D35" t="str">
-        <v>20/03/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="E35">
-        <v>148680</v>
+        <v>154580</v>
       </c>
       <c r="F35">
-        <v>126000</v>
+        <v>131000</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>11340</v>
+        <v>11790</v>
       </c>
       <c r="I35">
-        <v>11340</v>
+        <v>11790</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1883,22 +1883,22 @@
         <v>S18/2026/063</v>
       </c>
       <c r="D36" t="str">
-        <v>12/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="E36">
-        <v>146320</v>
+        <v>148680</v>
       </c>
       <c r="F36">
-        <v>124000</v>
+        <v>126000</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>11160</v>
+        <v>11340</v>
       </c>
       <c r="I36">
-        <v>11160</v>
+        <v>11340</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2026-04</v>
       </c>
       <c r="L36" t="str">
-        <v>15/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1930,16 +1930,16 @@
         <v>S19/2026/061</v>
       </c>
       <c r="D37" t="str">
-        <v>17/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="E37">
-        <v>103840</v>
+        <v>107380</v>
       </c>
       <c r="F37">
-        <v>88000</v>
+        <v>91000</v>
       </c>
       <c r="G37">
-        <v>15840</v>
+        <v>16380</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2026-04</v>
       </c>
       <c r="L37" t="str">
-        <v>14/04/2026</v>
+        <v>12/04/2026</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
@@ -1977,16 +1977,16 @@
         <v>S19/2026/062</v>
       </c>
       <c r="D38" t="str">
-        <v>09/03/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="E38">
-        <v>105020</v>
+        <v>109740</v>
       </c>
       <c r="F38">
-        <v>89000</v>
+        <v>93000</v>
       </c>
       <c r="G38">
-        <v>16020</v>
+        <v>16740</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2026-04</v>
       </c>
       <c r="L38" t="str">
-        <v>15/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2024,22 +2024,22 @@
         <v>S20/2026/061</v>
       </c>
       <c r="D39" t="str">
-        <v>07/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="E39">
-        <v>155760</v>
+        <v>145140</v>
       </c>
       <c r="F39">
-        <v>132000</v>
+        <v>123000</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>11880</v>
+        <v>11070</v>
       </c>
       <c r="I39">
-        <v>11880</v>
+        <v>11070</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2026-04</v>
       </c>
       <c r="L39" t="str">
-        <v>11/04/2026</v>
+        <v>09/04/2026</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2074,19 +2074,19 @@
         <v>23/03/2026</v>
       </c>
       <c r="E40">
-        <v>148680</v>
+        <v>136880</v>
       </c>
       <c r="F40">
-        <v>126000</v>
+        <v>116000</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>11340</v>
+        <v>10440</v>
       </c>
       <c r="I40">
-        <v>11340</v>
+        <v>10440</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2115,19 +2115,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C41" t="str">
-        <v>S21/2026/061</v>
+        <v>S21/2026/062</v>
       </c>
       <c r="D41" t="str">
-        <v>10/03/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="E41">
-        <v>199420</v>
+        <v>193520</v>
       </c>
       <c r="F41">
-        <v>169000</v>
+        <v>164000</v>
       </c>
       <c r="G41">
-        <v>30420</v>
+        <v>29520</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2026-04</v>
       </c>
       <c r="L41" t="str">
-        <v>10/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2162,19 +2162,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C42" t="str">
-        <v>S21/2026/062</v>
+        <v>S21/2026/063</v>
       </c>
       <c r="D42" t="str">
-        <v>08/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="E42">
-        <v>182900</v>
+        <v>186440</v>
       </c>
       <c r="F42">
-        <v>155000</v>
+        <v>158000</v>
       </c>
       <c r="G42">
-        <v>27900</v>
+        <v>28440</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2026-04</v>
       </c>
       <c r="L42" t="str">
-        <v>13/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="M42" t="str">
         <v>Yes</v>
@@ -2203,31 +2203,31 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>27AAGFM1167A1ZO</v>
       </c>
       <c r="B43" t="str">
-        <v>Nova Instruments</v>
+        <v>Meridian Housekeeping</v>
       </c>
       <c r="C43" t="str">
-        <v>S21/2026/063</v>
+        <v>S22/2026/051</v>
       </c>
       <c r="D43" t="str">
-        <v>17/03/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="E43">
-        <v>188800</v>
+        <v>195880</v>
       </c>
       <c r="F43">
-        <v>160000</v>
+        <v>166000</v>
       </c>
       <c r="G43">
-        <v>28800</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>14940</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>14940</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>2026-04</v>
       </c>
       <c r="L43" t="str">
-        <v>08/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
@@ -2259,22 +2259,22 @@
         <v>S22/2026/061</v>
       </c>
       <c r="D44" t="str">
-        <v>08/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="E44">
-        <v>197060</v>
+        <v>214760</v>
       </c>
       <c r="F44">
-        <v>167000</v>
+        <v>182000</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>15030</v>
+        <v>16380</v>
       </c>
       <c r="I44">
-        <v>15030</v>
+        <v>16380</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>2026-04</v>
       </c>
       <c r="L44" t="str">
-        <v>10/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="M44" t="str">
         <v>Yes</v>
@@ -2306,16 +2306,16 @@
         <v>S23/2026/061</v>
       </c>
       <c r="D45" t="str">
-        <v>06/03/2026</v>
+        <v>26/03/2026</v>
       </c>
       <c r="E45">
-        <v>188800</v>
+        <v>182900</v>
       </c>
       <c r="F45">
-        <v>160000</v>
+        <v>155000</v>
       </c>
       <c r="G45">
-        <v>28800</v>
+        <v>27900</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>2026-04</v>
       </c>
       <c r="L45" t="str">
-        <v>14/04/2026</v>
+        <v>12/04/2026</v>
       </c>
       <c r="M45" t="str">
         <v>Yes</v>
@@ -2353,16 +2353,16 @@
         <v>S24/2026/061</v>
       </c>
       <c r="D46" t="str">
-        <v>20/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="E46">
-        <v>146320</v>
+        <v>151040</v>
       </c>
       <c r="F46">
-        <v>124000</v>
+        <v>128000</v>
       </c>
       <c r="G46">
-        <v>22320</v>
+        <v>23040</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         <v>2026-04</v>
       </c>
       <c r="L46" t="str">
-        <v>16/04/2026</v>
+        <v>12/04/2026</v>
       </c>
       <c r="M46" t="str">
         <v>Yes</v>
@@ -2400,16 +2400,16 @@
         <v>S24/2026/062</v>
       </c>
       <c r="D47" t="str">
-        <v>09/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="E47">
-        <v>152220</v>
+        <v>147500</v>
       </c>
       <c r="F47">
-        <v>129000</v>
+        <v>125000</v>
       </c>
       <c r="G47">
-        <v>23220</v>
+        <v>22500</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>2026-04</v>
       </c>
       <c r="L47" t="str">
-        <v>10/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="M47" t="str">
         <v>Yes</v>
@@ -2447,16 +2447,16 @@
         <v>S24/2026/063</v>
       </c>
       <c r="D48" t="str">
-        <v>07/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="E48">
-        <v>169920</v>
+        <v>143960</v>
       </c>
       <c r="F48">
-        <v>144000</v>
+        <v>122000</v>
       </c>
       <c r="G48">
-        <v>25920</v>
+        <v>21960</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>2026-04</v>
       </c>
       <c r="L48" t="str">
-        <v>12/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="M48" t="str">
         <v>Yes</v>
@@ -2494,22 +2494,22 @@
         <v>S25/2026/061</v>
       </c>
       <c r="D49" t="str">
-        <v>09/03/2026</v>
+        <v>26/03/2026</v>
       </c>
       <c r="E49">
-        <v>49560</v>
+        <v>41300</v>
       </c>
       <c r="F49">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>3780</v>
+        <v>3150</v>
       </c>
       <c r="I49">
-        <v>3780</v>
+        <v>3150</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>2026-04</v>
       </c>
       <c r="L49" t="str">
-        <v>16/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="M49" t="str">
         <v>Yes</v>
